--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488231_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488231_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.8729</v>
+        <v>12.3843</v>
       </c>
       <c r="E2" t="n">
-        <v>12.7929</v>
+        <v>11.4766</v>
       </c>
       <c r="F2" t="n">
-        <v>1.08</v>
+        <v>0.9077</v>
       </c>
       <c r="G2" t="n">
         <v>4.5332</v>
@@ -610,13 +610,13 @@
         <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1931</v>
+        <v>0.7045</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1912</v>
+        <v>0.8749</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002</v>
+        <v>-0.1704</v>
       </c>
       <c r="V2" t="n">
         <v>5.6643</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6257</v>
+        <v>4.4902</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5664</v>
+        <v>4.1108</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0593</v>
+        <v>0.3794</v>
       </c>
       <c r="G3" t="n">
         <v>3.3296</v>
@@ -688,13 +688,13 @@
         <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0538</v>
+        <v>-0.1893</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4203</v>
+        <v>0.1241</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6335</v>
+        <v>-0.3134</v>
       </c>
       <c r="V3" t="n">
         <v>2.8321</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>B. LEÓN TEJERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8803</v>
+        <v>0.6221</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9336</v>
+        <v>0.6221</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.4166</v>
+        <v>0.6221</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2969</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1197</v>
+        <v>0.6221</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.1255</v>
+        <v>0.6221</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7736</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3519</v>
+        <v>0.6221</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2911</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5233</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7678</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6293</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1153</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5141</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. LEÓN TEJERA</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6221</v>
+        <v>0.0049</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6221</v>
+        <v>0.3783</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.3734</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6221</v>
+        <v>-3.4166</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-2.2969</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6221</v>
+        <v>-1.1197</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6221</v>
+        <v>-1.1255</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.7736</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6221</v>
+        <v>-0.3519</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-2.2911</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.5233</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.7678</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.7539</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.5599</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1867</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9683</v>
+        <v>-0.326</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2183</v>
+        <v>-0.5384</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3293</v>
@@ -922,13 +922,13 @@
         <v>1.297</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5255</v>
+        <v>-0.2033</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0396</v>
+        <v>-0.3973</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5141</v>
+        <v>0.194</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6289</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4239</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7129</v>
+        <v>1.3552</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1367</v>
+        <v>-2.2599</v>
       </c>
       <c r="G7" t="n">
         <v>1.7365</v>
@@ -1000,13 +1000,13 @@
         <v>1.4823</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8655</v>
+        <v>-0.3463</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8207</v>
+        <v>-0.1784</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0448</v>
+        <v>-0.1679</v>
       </c>
       <c r="V7" t="n">
         <v>-3.7771</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3501</v>
+        <v>-1.2399</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0743</v>
+        <v>-1.432</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2758</v>
+        <v>0.192</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6982</v>
@@ -1078,13 +1078,13 @@
         <v>2.4087</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2077</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5296999999999999</v>
+        <v>0.1126</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.678</v>
+        <v>-0.2102</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4754</v>
+        <v>-2.2948</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0517</v>
+        <v>-1.8219</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4236</v>
+        <v>-0.4729</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3653</v>
@@ -1156,13 +1156,13 @@
         <v>1.1117</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4245</v>
+        <v>0.7561</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7449</v>
+        <v>0.485</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3203</v>
+        <v>0.2711</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5579</v>
+        <v>-2.9397</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5046</v>
+        <v>-1.9602</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0533</v>
+        <v>-0.9794</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3671</v>
@@ -1234,13 +1234,13 @@
         <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7466</v>
+        <v>-0.1284</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5471</v>
+        <v>-0.0028</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1995</v>
+        <v>-0.1256</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2589</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0584</v>
+        <v>-4.7619</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8168</v>
+        <v>-2.6435</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2416</v>
+        <v>-2.1185</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9621</v>
@@ -1312,13 +1312,13 @@
         <v>2.0382</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6241</v>
+        <v>0.9205</v>
       </c>
       <c r="T11" t="n">
-        <v>1.593</v>
+        <v>0.7664</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0311</v>
+        <v>0.1542</v>
       </c>
       <c r="V11" t="n">
         <v>-2.8321</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.948600000000002</v>
+        <v>4.496099999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>9.212199999999999</v>
+        <v>9.759399999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.2633</v>
+        <v>-5.263400000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-2.917199999999999</v>
@@ -1390,10 +1390,10 @@
         <v>15.7493</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6229</v>
+        <v>2.1701</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7972</v>
+        <v>2.3444</v>
       </c>
       <c r="U12" t="n">
         <v>-0.1742</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4598</v>
+        <v>2.7109</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5045</v>
+        <v>2.0286</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0447</v>
+        <v>0.6823</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6144</v>
+        <v>1.5785</v>
       </c>
       <c r="H13" t="n">
-        <v>3.172</v>
+        <v>1.5756</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5576</v>
+        <v>0.0029</v>
       </c>
       <c r="J13" t="n">
-        <v>4.0462</v>
+        <v>2.242</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2677</v>
+        <v>1.4943</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7785</v>
+        <v>0.7477</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4318</v>
+        <v>-0.6635</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0813</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3361</v>
+        <v>-0.7448</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.594</v>
+        <v>1.1117</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.0763</v>
+        <v>-0.1853</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4823</v>
+        <v>1.297</v>
       </c>
       <c r="S13" t="n">
-        <v>2.125</v>
+        <v>-0.6087</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7024</v>
+        <v>-0.3426</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4225</v>
+        <v>-0.2661</v>
       </c>
       <c r="V13" t="n">
+        <v>0.6294</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.3144</v>
       </c>
-      <c r="W13" t="n">
-        <v>2.8321</v>
-      </c>
       <c r="X13" t="n">
-        <v>-2.5177</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0248</v>
+        <v>1.2674</v>
       </c>
       <c r="E14" t="n">
-        <v>1.441</v>
+        <v>3.3293</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5838</v>
+        <v>-2.0619</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5785</v>
+        <v>2.6144</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5756</v>
+        <v>3.172</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0029</v>
+        <v>-0.5576</v>
       </c>
       <c r="J14" t="n">
-        <v>2.242</v>
+        <v>4.0462</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4943</v>
+        <v>3.2677</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7477</v>
+        <v>0.7785</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6635</v>
+        <v>-1.4318</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0813</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7448</v>
+        <v>-1.3361</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1117</v>
+        <v>-2.594</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1853</v>
+        <v>-4.0763</v>
       </c>
       <c r="R14" t="n">
-        <v>1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2948</v>
+        <v>0.9326</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9302</v>
+        <v>0.5273</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3646</v>
+        <v>0.4054</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3144</v>
+        <v>2.8321</v>
       </c>
       <c r="X14" t="n">
-        <v>0.315</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. RUEDA MURIEL</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.555</v>
+        <v>1.2458</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0224</v>
+        <v>1.4356</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4674</v>
+        <v>-0.1898</v>
       </c>
       <c r="G15" t="n">
-        <v>0.633</v>
+        <v>-0.1474</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0075</v>
+        <v>0.014</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6405</v>
+        <v>-0.1614</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.998</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0215</v>
+        <v>0.6696</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6635</v>
+        <v>1.3283</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.052</v>
+        <v>-2.1454</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.029</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.023</v>
+        <v>-1.4897</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.6676</v>
+        <v>1.1117</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0382</v>
+        <v>-0.3706</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="S15" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.3485</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5434</v>
+        <v>-0.1918</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4716</v>
+        <v>-0.1567</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5177</v>
+        <v>0.63</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8321</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>M. RUEDA MURIEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4223</v>
+        <v>1.1387</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3418</v>
+        <v>1.6307</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0804</v>
+        <v>-0.492</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8098</v>
+        <v>0.633</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5616</v>
+        <v>-0.0075</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3714</v>
+        <v>0.6405</v>
       </c>
       <c r="J16" t="n">
-        <v>1.205</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9562</v>
+        <v>0.0215</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2488</v>
+        <v>0.6635</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0148</v>
+        <v>-0.052</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3945</v>
+        <v>-0.029</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6203</v>
+        <v>-0.023</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.0382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2147</v>
+        <v>-0.3445</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2873</v>
+        <v>0.1517</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9274</v>
+        <v>-0.4962</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5733</v>
+        <v>2.5177</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8877</v>
+        <v>2.8321</v>
       </c>
       <c r="X16" t="n">
         <v>-0.3144</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7309</v>
+        <v>0.8148</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2106</v>
+        <v>1.2439</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9415</v>
+        <v>-0.4292</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3705</v>
+        <v>-0.8098</v>
       </c>
       <c r="H17" t="n">
-        <v>0.329</v>
+        <v>0.5616</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0415</v>
+        <v>-1.3714</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0629</v>
+        <v>1.205</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0215</v>
+        <v>0.9562</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0415</v>
+        <v>0.2488</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3076</v>
+        <v>-2.0148</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3076</v>
+        <v>-0.3945</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1.6203</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1853</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1751</v>
+        <v>0.6071</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2736</v>
+        <v>0.1894</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4487</v>
+        <v>0.4178</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0616</v>
+        <v>0.6811</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5542</v>
+        <v>-0.1127</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6158</v>
+        <v>0.7938</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1474</v>
+        <v>0.3705</v>
       </c>
       <c r="H18" t="n">
-        <v>0.014</v>
+        <v>0.329</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1614</v>
+        <v>0.0415</v>
       </c>
       <c r="J18" t="n">
-        <v>1.998</v>
+        <v>0.0629</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6696</v>
+        <v>0.0215</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3283</v>
+        <v>0.0415</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1454</v>
+        <v>0.3076</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.3076</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4897</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4823</v>
+        <v>0.1853</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6559</v>
+        <v>0.1253</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0732</v>
+        <v>-0.1756</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5827</v>
+        <v>0.3009</v>
       </c>
       <c r="V18" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.673</v>
+        <v>-0.91</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3887</v>
+        <v>0.0949</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0616</v>
+        <v>-1.0049</v>
       </c>
       <c r="G19" t="n">
         <v>2.6047</v>
@@ -1936,13 +1936,13 @@
         <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2221</v>
+        <v>-0.4592</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3756</v>
+        <v>0.0818</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5977</v>
+        <v>-0.541</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5733</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.707</v>
+        <v>-1.2649</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7709</v>
+        <v>-0.575</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9361</v>
+        <v>-0.6899</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0564</v>
@@ -2014,13 +2014,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9476</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3283</v>
+        <v>-0.1324</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6193</v>
+        <v>-0.3731</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2589</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9114</v>
+        <v>-3.2494</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5072</v>
+        <v>-1.0176</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4042</v>
+        <v>-2.2318</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3946</v>
@@ -2092,13 +2092,13 @@
         <v>0.9264</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.0401</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4166</v>
+        <v>0.0731</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2855</v>
+        <v>-0.1132</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6294</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7886</v>
+        <v>-5.7302</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5005</v>
+        <v>-2.7943</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2881</v>
+        <v>-2.9359</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4757</v>
@@ -2170,13 +2170,13 @@
         <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.387</v>
+        <v>-0.3286</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2873</v>
+        <v>-0.0065</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6743</v>
+        <v>-0.3221</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8877</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9488</v>
+        <v>-3.2958</v>
       </c>
       <c r="E23" t="n">
         <v>5.263399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.212199999999999</v>
+        <v>-8.5593</v>
       </c>
       <c r="G23" t="n">
         <v>2.917199999999999</v>
@@ -2230,16 +2230,16 @@
         <v>1.5727</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.796000000000003</v>
+        <v>-8.795999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5798000000000002</v>
+        <v>-0.5798000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-8.2163</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.5587</v>
+        <v>-5.558699999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-15.7495</v>
@@ -2248,19 +2248,19 @@
         <v>10.1908</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6228</v>
+        <v>-0.9701</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1740999999999999</v>
+        <v>0.1744</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.7971</v>
+        <v>-1.1443</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3155000000000008</v>
+        <v>0.3155000000000003</v>
       </c>
       <c r="W23" t="n">
-        <v>9.125200000000001</v>
+        <v>9.1252</v>
       </c>
       <c r="X23" t="n">
         <v>-8.809699999999999</v>
